--- a/DATA/DATI_TESI.xlsx
+++ b/DATA/DATI_TESI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniroma2-my.sharepoint.com/personal/martino_cerilli_students_uniroma2_eu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martino\source\repos\Martix4335\TESI_MC\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6236D8F7-405C-4528-AA44-140DA5A2AA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A6AA86-24E6-4AA5-98B6-DEC79F5A3738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{CECD775E-E98E-44A0-BF85-38441AC3C535}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="5" xr2:uid="{CECD775E-E98E-44A0-BF85-38441AC3C535}"/>
   </bookViews>
   <sheets>
     <sheet name="CH1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="CH3" sheetId="3" r:id="rId3"/>
     <sheet name="CH4" sheetId="4" r:id="rId4"/>
     <sheet name="Result" sheetId="5" r:id="rId5"/>
+    <sheet name="CHANGED" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -279,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="10">
   <si>
     <t>V</t>
   </si>
@@ -315,7 +316,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,6 +375,223 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>462643</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>5443</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>462643</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>16329</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connettore 2 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0590CE8-0DFB-40ED-9EB9-E94691786442}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="462643" y="375557"/>
+          <a:ext cx="0" cy="195943"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>462643</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>5443</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>462643</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>16329</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Connettore 2 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B0759EB-8750-4769-81B5-44EB685ED89F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1115786" y="375557"/>
+          <a:ext cx="0" cy="195943"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>462643</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>5443</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>462643</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>16329</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Connettore 2 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3086F29B-042B-4B6C-B9BD-EF1FD0624CE5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1768929" y="375557"/>
+          <a:ext cx="0" cy="195943"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>462643</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>5443</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>462643</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>16329</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Connettore 2 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97A5FF9D-2C72-4206-8253-03CCA4FB0779}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2422072" y="375557"/>
+          <a:ext cx="0" cy="195943"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -694,9 +912,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0D3E70-F390-4A94-BC3C-84BD8C8064DB}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -725,7 +943,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1500</v>
       </c>
@@ -755,7 +973,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1600</v>
       </c>
@@ -776,7 +994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1700</v>
       </c>
@@ -797,7 +1015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1800</v>
       </c>
@@ -818,7 +1036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1900</v>
       </c>
@@ -839,7 +1057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>2000</v>
       </c>
@@ -860,7 +1078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>2100</v>
       </c>
@@ -890,9 +1108,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F91A0EE-81D0-44A3-A14B-495972015FA9}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -921,7 +1139,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1500</v>
       </c>
@@ -951,7 +1169,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1600</v>
       </c>
@@ -972,7 +1190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1700</v>
       </c>
@@ -993,7 +1211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1800</v>
       </c>
@@ -1014,7 +1232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1900</v>
       </c>
@@ -1035,7 +1253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>2000</v>
       </c>
@@ -1056,7 +1274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>2100</v>
       </c>
@@ -1077,7 +1295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>2200</v>
       </c>
@@ -1107,9 +1325,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4397002-08AE-4F77-9934-CB2EC1521FA3}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1138,7 +1356,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1500</v>
       </c>
@@ -1168,7 +1386,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1600</v>
       </c>
@@ -1179,7 +1397,7 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D9" si="0">SQRT(C3)</f>
+        <f t="shared" ref="D3:D7" si="0">SQRT(C3)</f>
         <v>4.1231056256176606</v>
       </c>
       <c r="E3">
@@ -1189,7 +1407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1700</v>
       </c>
@@ -1210,7 +1428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1800</v>
       </c>
@@ -1231,7 +1449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1900</v>
       </c>
@@ -1252,7 +1470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>2000</v>
       </c>
@@ -1282,9 +1500,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F170572-6B9B-45C8-BC60-E1EBC84AC892}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1313,7 +1531,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1500</v>
       </c>
@@ -1343,7 +1561,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1600</v>
       </c>
@@ -1364,7 +1582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1700</v>
       </c>
@@ -1385,7 +1603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1800</v>
       </c>
@@ -1406,7 +1624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1900</v>
       </c>
@@ -1427,7 +1645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>2000</v>
       </c>
@@ -1457,9 +1675,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FCE112D-8D04-4840-8ED7-47789AC285A9}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1473,7 +1691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1950</v>
       </c>
@@ -1492,7 +1710,68 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92AFA0EC-7E04-4090-B752-D85236F389F3}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>1950</v>
+      </c>
+      <c r="B2">
+        <v>2100</v>
+      </c>
+      <c r="C2">
+        <v>1850</v>
+      </c>
+      <c r="D2">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>2050</v>
+      </c>
+      <c r="B4">
+        <v>2100</v>
+      </c>
+      <c r="C4">
+        <v>1950</v>
+      </c>
+      <c r="D4">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7e0aec07-c6f4-4280-8b8c-b8ba178e9f3c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CFE6BEF1BD9BA845B6EE1D2BBFF8C22F" ma:contentTypeVersion="6" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="208af788fbcac1c89764b6e21c748a2e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7e0aec07-c6f4-4280-8b8c-b8ba178e9f3c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b1b5010e96f6343d3d520804e870157" ns3:_="">
     <xsd:import namespace="7e0aec07-c6f4-4280-8b8c-b8ba178e9f3c"/>
@@ -1648,14 +1927,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7e0aec07-c6f4-4280-8b8c-b8ba178e9f3c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1666,13 +1937,37 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E3DB407-1778-4353-B07B-49BDFE079E38}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D52C255-6E98-4353-B0B5-47EF9FF6160D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7e0aec07-c6f4-4280-8b8c-b8ba178e9f3c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D52C255-6E98-4353-B0B5-47EF9FF6160D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E3DB407-1778-4353-B07B-49BDFE079E38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7e0aec07-c6f4-4280-8b8c-b8ba178e9f3c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86F56F28-2FB4-4CD0-9BF9-A5094705089C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86F56F28-2FB4-4CD0-9BF9-A5094705089C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>